--- a/stories/arbres/TREE-EMO-006.xlsx
+++ b/stories/arbres/TREE-EMO-006.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le chemin de l'école, Lila tient la main de papa. Un orage gronde, loin. Le ventre de Lila se serre. Les épaules montent. Maman a mis le goûter dans le sac. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Les cubes tremblent dans le sac. Lila se sent inquiète. le ventre serré. Voici les cubes. Ça sent le thym du jardin. Lila s'approche, sans courir. Maman n'est pas loin. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le ventre de Lila est serré. Que fait-on ? Avec les cubes.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi une pomme, après les cubes. Le banc est tiède. Lila attend près de une pomme. Elle ne prend pas de force. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2579,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2746,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après les cubes et une pomme. La tasse est encore tiède. On dit merci. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chat un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2913,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3080,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après les cubes et une pomme. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila boit une gorgée. Elle se sent plus légère. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3247,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3414,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après les cubes et une pomme. Une abeille bourdonne loin. On attend un petit moment. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila dit merci à papa. Maman sourit. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3581,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3748,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un yaourt, après les cubes. La cuillère tinte. Lila choisit un yaourt. Maman n'est pas loin. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3939,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4106,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après les cubes et un yaourt. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chat un instant. Puis elle reprend, calme. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4273,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4440,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après les cubes et un yaourt. La fenêtre tremble un tout petit peu. On sourit un peu. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila boit une gorgée. Elle se sent plus légère. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4607,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4774,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après les cubes et un yaourt. Ça sent le savon de maman. On boit une gorgée d'eau. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila dit merci à papa. Maman sourit. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4941,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5108,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un morceau de pain, après les cubes. Ça sent la pomme. Lila montre un morceau de pain à papa. Elle nomme ce qu'elle sent. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5299,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5466,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après les cubes et un morceau de pain. Un pigeon roucoule. On essuie une miette. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On écoute le silence une seconde. Lila est assise. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5633,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5515,7 +5662,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Lila rejoint le chien, après les cubes et un morceau de pain. La cuillère tinte. On referme un livre. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Papa dit : je t'ai entendu. Maman aussi. On rentre.</t>
+          <t>Lila rejoint le chien, après les cubes et un morceau de pain. La cuillère tinte. On referme un livre. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5653,6 +5800,12 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après les cubes et un morceau de pain. La cuillère tinte. On referme un livre. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.
+papa|Je t'ai entendu. Maman aussi. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après les cubes et un morceau de pain. Le ballon est un peu poudreux. On pose un jouet à sa place. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On laisse la poule à sa place. Lila est près de papa. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6469,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Le livre tombe. Lila se sent inquiète. Lila s'occupe du livre. Le train souffle au loin. Papa sourit. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6650,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Le ventre de Lila est serré. Que fait-on ? Avec le livre.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6823,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila répète le mot. Papa hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7014,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7181,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi une pomme, après le livre. Un grillon chante, tout petit. Une pomme reste à sa place. Lila aussi. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7372,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7539,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le livre et une pomme. Une goutte de pluie sèche déjà. On marche tout doucement. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila pose le chat et va vers papa. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7706,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7873,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le livre et une pomme. Le banc est tiède. On se tait une seconde. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila dit merci à papa. Maman sourit. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8040,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8207,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le livre et une pomme. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila boit une gorgée. Elle se sent plus légère. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8374,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8541,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un yaourt, après le livre. Les chaussures font un bruit léger. Lila s'installe avec un yaourt. Papa reste à portée de voix. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8732,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8899,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le livre et un yaourt. Une feuille tourne et tombe. On s'assoit près de l'adulte. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila serre la main de papa, tout doux. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9066,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9233,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le livre et un yaourt. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chien un instant. Puis elle reprend, calme. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9400,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9567,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le livre et un yaourt. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila dit merci à papa. Maman sourit. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9734,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9901,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un morceau de pain, après le livre. Le sable colle un peu aux doigts. Lila attend près de un morceau de pain. Elle ne prend pas de force. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10092,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10259,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après le livre et un morceau de pain. Une plume vole. On range les chaussures. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10426,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10593,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après le livre et un morceau de pain. Le pain croustille. On met le doudou près de soi. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila boit une gorgée. Elle se sent plus légère. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10760,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10927,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après le livre et un morceau de pain. La laine du doudou est douce. On écoute le cœur, tout doux. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue la poule un instant. Puis elle reprend, calme. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11094,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11261,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|La dînette cliquette. Lila se sent inquiète. Voilà la dînette. Le seau sonne, tout léger. Lila pose les pieds par terre, près de papa. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11442,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Le ventre de Lila est serré. Que fait-on ? Avec la dînette.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11615,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11806,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11973,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi une pomme, après la dînette. Le lait est tiède. Avec une pomme, Lila ralentit. Elle écoute papa. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12164,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12331,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après la dînette et une pomme. Un galet est lisse dans la main. On secoue les mains, loin. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chat un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12498,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12665,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après la dînette et une pomme. Le train souffle au loin. On pose le sac. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On écoute le silence une seconde. Lila est assise. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12832,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +12999,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après la dînette et une pomme. Une vache meugle, loin. On dit le mot de l'émotion. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On écoute le silence une seconde. Lila est assise. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13166,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13333,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un yaourt, après la dînette. La corde de la balançoire bouge. Lila montre un yaourt à papa. Elle nomme ce qu'elle sent. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13524,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13691,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après la dînette et un yaourt. Un grillon chante, tout petit. On invite d'une petite voix. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chat un instant. Puis elle reprend, calme. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13858,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14025,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après la dînette et un yaourt. Le bois de la table est lisse. On attend la réponse. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chien un instant. Puis elle reprend, calme. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14192,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14359,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après la dînette et un yaourt. Une goutte tombe dans l'évier. On propose une autre idée. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On écoute le silence une seconde. Lila est assise. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14526,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14693,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a choisi un morceau de pain, après la dînette. Le banc est tiède. Lila montre un morceau de pain à papa. Elle nomme ce qu'elle sent. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14884,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15051,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chat, après la dînette et un morceau de pain. Le toboggan est un peu froid. On va vers papa ou maman. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila pose le chat et va vers papa. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15218,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15385,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint le chien, après la dînette et un morceau de pain. La clochette de la porte tinte. On dit stop, tout clair. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila pose le chien et va vers papa. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15552,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15719,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lila rejoint la poule, après la dînette et un morceau de pain. Ça sent le thym du jardin. On s'éloigne d'un pas. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue la poule un instant. Puis elle reprend, calme. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15886,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15926,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-006.xlsx
+++ b/stories/arbres/TREE-EMO-006.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Sur le chemin de l'école, Lila tient la main de papa. Un orage gronde, loin. Le ventre de Lila se serre. Les épaules montent. Maman a mis le goûter dans le sac. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Les cubes tremblent dans le sac. Lila se sent inquiète. le ventre serré. Voici les cubes. Ça sent le thym du jardin. Lila s'approche, sans courir. Maman n'est pas loin. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Le ventre de Lila est serré. Que fait-on ? Avec les cubes.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Oui. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Lila a choisi une pomme, après les cubes. Le banc est tiède. Lila attend près de une pomme. Elle ne prend pas de force. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2582,6 +2594,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2751,6 +2768,7 @@
           <t>narrateur|Lila rejoint le chat, après les cubes et une pomme. La tasse est encore tiède. On dit merci. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chat un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2918,6 +2936,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3085,6 +3104,11 @@
           <t>narrateur|Lila rejoint le chien, après les cubes et une pomme. Le parquet craque un tout petit peu. On écoute jusqu'au bout. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila boit une gorgée. Elle se sent plus légère. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3252,6 +3276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3419,6 +3444,7 @@
           <t>narrateur|Lila rejoint la poule, après les cubes et une pomme. Une abeille bourdonne loin. On attend un petit moment. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila dit merci à papa. Maman sourit. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3586,6 +3612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3753,6 +3780,7 @@
           <t>narrateur|Lila a choisi un yaourt, après les cubes. La cuillère tinte. Lila choisit un yaourt. Maman n'est pas loin. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3942,6 +3970,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4111,6 +4144,7 @@
           <t>narrateur|Lila rejoint le chat, après les cubes et un yaourt. Un gravier roule sous une semelle. On pose les fesses sur une chaise. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chat un instant. Puis elle reprend, calme. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4278,6 +4312,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4445,6 +4480,11 @@
           <t>narrateur|Lila rejoint le chien, après les cubes et un yaourt. La fenêtre tremble un tout petit peu. On sourit un peu. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila boit une gorgée. Elle se sent plus légère. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4612,6 +4652,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4779,6 +4820,7 @@
           <t>narrateur|Lila rejoint la poule, après les cubes et un yaourt. Ça sent le savon de maman. On boit une gorgée d'eau. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila dit merci à papa. Maman sourit. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4946,6 +4988,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5113,6 +5156,7 @@
           <t>narrateur|Lila a choisi un morceau de pain, après les cubes. Ça sent la pomme. Lila montre un morceau de pain à papa. Elle nomme ce qu'elle sent. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5302,6 +5346,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5471,6 +5520,7 @@
           <t>narrateur|Lila rejoint le chat, après les cubes et un morceau de pain. Un pigeon roucoule. On essuie une miette. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On écoute le silence une seconde. Lila est assise. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5638,6 +5688,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5857,11 @@
 papa|Je t'ai entendu. Maman aussi. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6197,7 @@
           <t>narrateur|Lila rejoint la poule, après les cubes et un morceau de pain. Le ballon est un peu poudreux. On pose un jouet à sa place. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On laisse la poule à sa place. Lila est près de papa. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6365,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6474,6 +6533,7 @@
           <t>narrateur|Le livre tombe. Lila se sent inquiète. Lila s'occupe du livre. Le train souffle au loin. Papa sourit. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6657,6 +6717,7 @@
           <t>narrateur|Le ventre de Lila est serré. Que fait-on ? Avec le livre.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6828,6 +6889,7 @@
           <t>narrateur|Oui. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila répète le mot. Papa hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7019,6 +7081,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7186,6 +7249,7 @@
           <t>narrateur|Lila a choisi une pomme, après le livre. Un grillon chante, tout petit. Une pomme reste à sa place. Lila aussi. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7375,6 +7439,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7544,6 +7613,7 @@
           <t>narrateur|Lila rejoint le chat, après le livre et une pomme. Une goutte de pluie sèche déjà. On marche tout doucement. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila pose le chat et va vers papa. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7711,6 +7781,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7878,6 +7949,11 @@
           <t>narrateur|Lila rejoint le chien, après le livre et une pomme. Le banc est tiède. On se tait une seconde. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila dit merci à papa. Maman sourit. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8045,6 +8121,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8212,6 +8289,7 @@
           <t>narrateur|Lila rejoint la poule, après le livre et une pomme. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila boit une gorgée. Elle se sent plus légère. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8379,6 +8457,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8546,6 +8625,7 @@
           <t>narrateur|Lila a choisi un yaourt, après le livre. Les chaussures font un bruit léger. Lila s'installe avec un yaourt. Papa reste à portée de voix. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8735,6 +8815,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8904,6 +8989,7 @@
           <t>narrateur|Lila rejoint le chat, après le livre et un yaourt. Une feuille tourne et tombe. On s'assoit près de l'adulte. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila serre la main de papa, tout doux. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9071,6 +9157,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9238,6 +9325,11 @@
           <t>narrateur|Lila rejoint le chien, après le livre et un yaourt. L'eau fait un tout petit bruit. On nomme ce qu'on sent. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chien un instant. Puis elle reprend, calme. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9405,6 +9497,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9572,6 +9665,7 @@
           <t>narrateur|Lila rejoint la poule, après le livre et un yaourt. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila dit merci à papa. Maman sourit. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9739,6 +9833,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9906,6 +10001,7 @@
           <t>narrateur|Lila a choisi un morceau de pain, après le livre. Le sable colle un peu aux doigts. Lila attend près de un morceau de pain. Elle ne prend pas de force. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10095,6 +10191,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10264,6 +10365,7 @@
           <t>narrateur|Lila rejoint le chat, après le livre et un morceau de pain. Une plume vole. On range les chaussures. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila nomme encore le mot, tout bas. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10431,6 +10533,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10598,6 +10701,11 @@
           <t>narrateur|Lila rejoint le chien, après le livre et un morceau de pain. Le pain croustille. On met le doudou près de soi. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila boit une gorgée. Elle se sent plus légère. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10765,6 +10873,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10932,6 +11041,7 @@
           <t>narrateur|Lila rejoint la poule, après le livre et un morceau de pain. La laine du doudou est douce. On écoute le cœur, tout doux. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue la poule un instant. Puis elle reprend, calme. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11099,6 +11209,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11266,6 +11377,7 @@
           <t>narrateur|La dînette cliquette. Lila se sent inquiète. Voilà la dînette. Le seau sonne, tout léger. Lila pose les pieds par terre, près de papa. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11449,6 +11561,7 @@
           <t>narrateur|Le ventre de Lila est serré. Que fait-on ? Avec la dînette.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11620,6 +11733,7 @@
           <t>narrateur|Oui. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11811,6 +11925,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11978,6 +12093,7 @@
           <t>narrateur|Lila a choisi une pomme, après la dînette. Le lait est tiède. Avec une pomme, Lila ralentit. Elle écoute papa. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12167,6 +12283,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12336,6 +12457,7 @@
           <t>narrateur|Lila rejoint le chat, après la dînette et une pomme. Un galet est lisse dans la main. On secoue les mains, loin. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chat un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12503,6 +12625,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12670,6 +12793,11 @@
           <t>narrateur|Lila rejoint le chien, après la dînette et une pomme. Le train souffle au loin. On pose le sac. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On écoute le silence une seconde. Lila est assise. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12837,6 +12965,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13004,6 +13133,7 @@
           <t>narrateur|Lila rejoint la poule, après la dînette et une pomme. Une vache meugle, loin. On dit le mot de l'émotion. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On écoute le silence une seconde. Lila est assise. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13171,6 +13301,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13338,6 +13469,7 @@
           <t>narrateur|Lila a choisi un yaourt, après la dînette. La corde de la balançoire bouge. Lila montre un yaourt à papa. Elle nomme ce qu'elle sent. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13527,6 +13659,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13696,6 +13833,7 @@
           <t>narrateur|Lila rejoint le chat, après la dînette et un yaourt. Un grillon chante, tout petit. On invite d'une petite voix. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chat un instant. Puis elle reprend, calme. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13863,6 +14001,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14030,6 +14169,11 @@
           <t>narrateur|Lila rejoint le chien, après la dînette et un yaourt. Le bois de la table est lisse. On attend la réponse. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue le chien un instant. Puis elle reprend, calme. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14197,6 +14341,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14364,6 +14509,7 @@
           <t>narrateur|Lila rejoint la poule, après la dînette et un yaourt. Une goutte tombe dans l'évier. On propose une autre idée. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. On écoute le silence une seconde. Lila est assise. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14531,6 +14677,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14698,6 +14845,7 @@
           <t>narrateur|Lila a choisi un morceau de pain, après la dînette. Le banc est tiède. Lila montre un morceau de pain à papa. Elle nomme ce qu'elle sent. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14887,6 +15035,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15056,6 +15209,7 @@
           <t>narrateur|Lila rejoint le chat, après la dînette et un morceau de pain. Le toboggan est un peu froid. On va vers papa ou maman. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila pose le chat et va vers papa. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15223,6 +15377,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15390,6 +15545,11 @@
           <t>narrateur|Lila rejoint le chien, après la dînette et un morceau de pain. La clochette de la porte tinte. On dit stop, tout clair. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila pose le chien et va vers papa. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15557,6 +15717,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15724,6 +15885,7 @@
           <t>narrateur|Lila rejoint la poule, après la dînette et un morceau de pain. Ça sent le thym du jardin. On s'éloigne d'un pas. Le nom de l'émotion, c'est inquiet. Lila se sent inquiète. Le ventre est serré. Lila rejoint un adulte. Elle raconte à papa. Lila salue la poule un instant. Puis elle reprend, calme. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15891,6 +16053,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15909,7 +16072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15933,6 +16096,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15947,7 +16124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16134,6 +16311,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
